--- a/files/九龙-启德-Monaco Marine.xlsx
+++ b/files/九龙-启德-Monaco Marine.xlsx
@@ -27544,7 +27544,7 @@
         </is>
       </c>
       <c r="E435" s="4" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F435" s="3" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>13733000</v>
       </c>
       <c r="I435" s="5" t="n">
-        <v>26158</v>
+        <v>26208</v>
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>13733000</v>
       </c>
       <c r="L435" s="5" t="n">
-        <v>26158</v>
+        <v>26208</v>
       </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
@@ -39517,9 +39517,9 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>A | 525呎 (2房)
+          <t>A | 524呎 (2房)
 $1373万
-$26,158/呎
+$26,208/呎
 (23年-12月-19日)</t>
         </is>
       </c>

--- a/files/九龙-启德-Monaco Marine.xlsx
+++ b/files/九龙-启德-Monaco Marine.xlsx
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -769,14 +769,14 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
         <v>8799000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>26826</v>
+        <v>26908</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>8799000</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>26826</v>
+        <v>26908</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>17036000</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>27656</v>
+        <v>27611</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>17036000</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>27656</v>
+        <v>27611</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
@@ -35593,10 +35593,10 @@
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>H | 328呎 (1房)
+          <t>H | 327呎 (1房)
 $880万
-$26,826/呎
-(26年-09月-02日)</t>
+$26,908/呎
+(26年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -36902,9 +36902,9 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>C | 616呎 (3房)
+          <t>C | 617呎 (3房)
 $1704万
-$27,656/呎
+$27,611/呎
 (22年-05月-20日)</t>
         </is>
       </c>

--- a/files/九龙-启德-Monaco Marine.xlsx
+++ b/files/九龙-启德-Monaco Marine.xlsx
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>20306000</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>28480</v>
+        <v>28440</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>20306000</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>28480</v>
+        <v>28440</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
@@ -36318,9 +36318,9 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 713呎 (3房)
+          <t>A | 714呎 (3房)
 $2031万
-$28,480/呎
+$28,440/呎
 (22年-05月-18日)</t>
         </is>
       </c>

--- a/files/九龙-启德-Monaco Marine.xlsx
+++ b/files/九龙-启德-Monaco Marine.xlsx
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="E386" s="4" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>14127000</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>26909</v>
+        <v>26960</v>
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>14127000</v>
       </c>
       <c r="L386" s="5" t="n">
-        <v>26909</v>
+        <v>26960</v>
       </c>
       <c r="M386" s="3" t="inlineStr">
         <is>
@@ -39076,9 +39076,9 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>A | 525呎 (2房)
+          <t>A | 524呎 (2房)
 $1413万
-$26,909/呎
+$26,960/呎
 (22年-05月-18日)</t>
         </is>
       </c>

--- a/files/九龙-启德-Monaco Marine.xlsx
+++ b/files/九龙-启德-Monaco Marine.xlsx
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>8799000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>26908</v>
+        <v>26826</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>8799000</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>26908</v>
+        <v>26826</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>8988000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>27486</v>
+        <v>27402</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>8988000</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>27486</v>
+        <v>27402</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>18132000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>29387</v>
+        <v>29435</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>18132000</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>29387</v>
+        <v>29435</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>20986000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>29392</v>
+        <v>29433</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>20986000</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>29392</v>
+        <v>29433</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>8781000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>26853</v>
+        <v>26771</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>8781000</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>26853</v>
+        <v>26771</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>8970000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>27431</v>
+        <v>27348</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>8970000</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>27431</v>
+        <v>27348</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>8960000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>27401</v>
+        <v>27317</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>8960000</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>27401</v>
+        <v>27317</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>8951000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>27373</v>
+        <v>27290</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>8951000</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>27373</v>
+        <v>27290</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>8939000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>27336</v>
+        <v>27253</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>8939000</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>27336</v>
+        <v>27253</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>17369000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>28151</v>
+        <v>28196</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>17369000</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>28151</v>
+        <v>28196</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>8925000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>27294</v>
+        <v>27210</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>8925000</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>27294</v>
+        <v>27210</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>20042000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>28070</v>
+        <v>28109</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>20042000</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>28070</v>
+        <v>28109</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>19983000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>27987</v>
+        <v>28027</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>19983000</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>27987</v>
+        <v>28027</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>8894000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>27199</v>
+        <v>27116</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>8894000</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>27199</v>
+        <v>27116</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>17660000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>28622</v>
+        <v>28669</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>17660000</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>28622</v>
+        <v>28669</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>8681000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>26547</v>
+        <v>26466</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>8681000</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>26547</v>
+        <v>26466</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>17554000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>28451</v>
+        <v>28497</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>17554000</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>28451</v>
+        <v>28497</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>8664000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>26495</v>
+        <v>26415</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>8664000</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>26495</v>
+        <v>26415</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>20306000</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>28440</v>
+        <v>28480</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>20306000</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>28440</v>
+        <v>28480</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>8953000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>27379</v>
+        <v>27296</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>8953000</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>27379</v>
+        <v>27296</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>8813000</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>26951</v>
+        <v>26869</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>8813000</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>26951</v>
+        <v>26869</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>16917000</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>27418</v>
+        <v>27463</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>16917000</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>27418</v>
+        <v>27463</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>8777000</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>26841</v>
+        <v>26759</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>8777000</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>26841</v>
+        <v>26759</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>17345000</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>28112</v>
+        <v>28157</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>17345000</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>28112</v>
+        <v>28157</v>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>8680000</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>26544</v>
+        <v>26463</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>8680000</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>26544</v>
+        <v>26463</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>17293000</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>28028</v>
+        <v>28073</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>17293000</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>28028</v>
+        <v>28073</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>8662000</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>26489</v>
+        <v>26409</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>8662000</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>26489</v>
+        <v>26409</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>19980000</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>27983</v>
+        <v>28022</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>19980000</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>27983</v>
+        <v>28022</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>19974000</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>27975</v>
+        <v>28014</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>19974000</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>27975</v>
+        <v>28014</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>8676000</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>26532</v>
+        <v>26451</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>8676000</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>26532</v>
+        <v>26451</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>16665000</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>27010</v>
+        <v>27054</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>16665000</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>27010</v>
+        <v>27054</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>19865000</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>27822</v>
+        <v>27861</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>19865000</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>27822</v>
+        <v>27861</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>8466000</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>25890</v>
+        <v>25811</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>8466000</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>25890</v>
+        <v>25811</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>17036000</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>27611</v>
+        <v>27656</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>17036000</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>27611</v>
+        <v>27656</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="E166" s="4" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>16861000</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>27327</v>
+        <v>27372</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>16861000</v>
       </c>
       <c r="L166" s="5" t="n">
-        <v>27327</v>
+        <v>27372</v>
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>18898000</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>26468</v>
+        <v>26505</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>18898000</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>26468</v>
+        <v>26505</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>8569000</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>26205</v>
+        <v>26125</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>8569000</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>26205</v>
+        <v>26125</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         </is>
       </c>
       <c r="E185" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>8422000</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>25755</v>
+        <v>25677</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>8422000</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>25755</v>
+        <v>25677</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         </is>
       </c>
       <c r="E193" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>8421000</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>25752</v>
+        <v>25674</v>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
         <v>8421000</v>
       </c>
       <c r="L193" s="5" t="n">
-        <v>25752</v>
+        <v>25674</v>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         </is>
       </c>
       <c r="E201" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>8562000</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>26183</v>
+        <v>26104</v>
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>8562000</v>
       </c>
       <c r="L201" s="5" t="n">
-        <v>26183</v>
+        <v>26104</v>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="E208" s="4" t="n">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>18350000</v>
       </c>
       <c r="I208" s="5" t="n">
-        <v>25700</v>
+        <v>25736</v>
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>18350000</v>
       </c>
       <c r="L208" s="5" t="n">
-        <v>25700</v>
+        <v>25736</v>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         </is>
       </c>
       <c r="E209" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>8316000</v>
       </c>
       <c r="I209" s="5" t="n">
-        <v>25431</v>
+        <v>25354</v>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>8316000</v>
       </c>
       <c r="L209" s="5" t="n">
-        <v>25431</v>
+        <v>25354</v>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         </is>
       </c>
       <c r="E216" s="4" t="n">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>18088000</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>25333</v>
+        <v>25369</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>18088000</v>
       </c>
       <c r="L216" s="5" t="n">
-        <v>25333</v>
+        <v>25369</v>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E217" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>8580000</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>26239</v>
+        <v>26159</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>8580000</v>
       </c>
       <c r="L217" s="5" t="n">
-        <v>26239</v>
+        <v>26159</v>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         </is>
       </c>
       <c r="E224" s="4" t="n">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>18078000</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>25319</v>
+        <v>25355</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>18078000</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>25319</v>
+        <v>25355</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         </is>
       </c>
       <c r="E225" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>8391000</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>25661</v>
+        <v>25582</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>8391000</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>25661</v>
+        <v>25582</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>8577000</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>26229</v>
+        <v>26149</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>8577000</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>26229</v>
+        <v>26149</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         </is>
       </c>
       <c r="E245" s="4" t="n">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>11755000</v>
       </c>
       <c r="I245" s="5" t="n">
-        <v>26298</v>
+        <v>26357</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>11755000</v>
       </c>
       <c r="L245" s="5" t="n">
-        <v>26298</v>
+        <v>26357</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="E256" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>11742000</v>
       </c>
       <c r="I256" s="5" t="n">
-        <v>26093</v>
+        <v>26151</v>
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>11742000</v>
       </c>
       <c r="L256" s="5" t="n">
-        <v>26093</v>
+        <v>26151</v>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         </is>
       </c>
       <c r="E263" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>12124000</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>26942</v>
+        <v>27002</v>
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>12124000</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>26942</v>
+        <v>27002</v>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="E270" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>11672000</v>
       </c>
       <c r="I270" s="5" t="n">
-        <v>25938</v>
+        <v>25996</v>
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>11672000</v>
       </c>
       <c r="L270" s="5" t="n">
-        <v>25938</v>
+        <v>25996</v>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         </is>
       </c>
       <c r="E277" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>11637000</v>
       </c>
       <c r="I277" s="5" t="n">
-        <v>25860</v>
+        <v>25918</v>
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>11637000</v>
       </c>
       <c r="L277" s="5" t="n">
-        <v>25860</v>
+        <v>25918</v>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         </is>
       </c>
       <c r="E284" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>11602000</v>
       </c>
       <c r="I284" s="5" t="n">
-        <v>25782</v>
+        <v>25840</v>
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>11602000</v>
       </c>
       <c r="L284" s="5" t="n">
-        <v>25782</v>
+        <v>25840</v>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         </is>
       </c>
       <c r="E288" s="4" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>15053000</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>28727</v>
+        <v>28672</v>
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>15053000</v>
       </c>
       <c r="L288" s="5" t="n">
-        <v>28727</v>
+        <v>28672</v>
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         </is>
       </c>
       <c r="E291" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>11567000</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>25704</v>
+        <v>25762</v>
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>11567000</v>
       </c>
       <c r="L291" s="5" t="n">
-        <v>25704</v>
+        <v>25762</v>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         </is>
       </c>
       <c r="E298" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>11533000</v>
       </c>
       <c r="I298" s="5" t="n">
-        <v>25629</v>
+        <v>25686</v>
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>11533000</v>
       </c>
       <c r="L298" s="5" t="n">
-        <v>25629</v>
+        <v>25686</v>
       </c>
       <c r="M298" s="3" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         </is>
       </c>
       <c r="E305" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F305" s="3" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>11498000</v>
       </c>
       <c r="I305" s="5" t="n">
-        <v>25551</v>
+        <v>25608</v>
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>11498000</v>
       </c>
       <c r="L305" s="5" t="n">
-        <v>25551</v>
+        <v>25608</v>
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         </is>
       </c>
       <c r="E319" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>11382000</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>25293</v>
+        <v>25350</v>
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>11382000</v>
       </c>
       <c r="L319" s="5" t="n">
-        <v>25293</v>
+        <v>25350</v>
       </c>
       <c r="M319" s="3" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         </is>
       </c>
       <c r="E323" s="4" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>14834000</v>
       </c>
       <c r="I323" s="5" t="n">
-        <v>28309</v>
+        <v>28255</v>
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>14834000</v>
       </c>
       <c r="L323" s="5" t="n">
-        <v>28309</v>
+        <v>28255</v>
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         </is>
       </c>
       <c r="E330" s="4" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>15145000</v>
       </c>
       <c r="I330" s="5" t="n">
-        <v>28903</v>
+        <v>28848</v>
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>15145000</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>28903</v>
+        <v>28848</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         </is>
       </c>
       <c r="E333" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F333" s="3" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>11314000</v>
       </c>
       <c r="I333" s="5" t="n">
-        <v>25142</v>
+        <v>25198</v>
       </c>
       <c r="J333" s="3" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>11314000</v>
       </c>
       <c r="L333" s="5" t="n">
-        <v>25142</v>
+        <v>25198</v>
       </c>
       <c r="M333" s="3" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         </is>
       </c>
       <c r="E344" s="4" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>14962000</v>
       </c>
       <c r="I344" s="5" t="n">
-        <v>28553</v>
+        <v>28499</v>
       </c>
       <c r="J344" s="3" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>14962000</v>
       </c>
       <c r="L344" s="5" t="n">
-        <v>28553</v>
+        <v>28499</v>
       </c>
       <c r="M344" s="3" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         </is>
       </c>
       <c r="E347" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>11247000</v>
       </c>
       <c r="I347" s="5" t="n">
-        <v>24993</v>
+        <v>25049</v>
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>11247000</v>
       </c>
       <c r="L347" s="5" t="n">
-        <v>24993</v>
+        <v>25049</v>
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         </is>
       </c>
       <c r="E354" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>11213000</v>
       </c>
       <c r="I354" s="5" t="n">
-        <v>24918</v>
+        <v>24973</v>
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>11213000</v>
       </c>
       <c r="L354" s="5" t="n">
-        <v>24918</v>
+        <v>24973</v>
       </c>
       <c r="M354" s="3" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="E361" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>11179000</v>
       </c>
       <c r="I361" s="5" t="n">
-        <v>24842</v>
+        <v>24898</v>
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>11179000</v>
       </c>
       <c r="L361" s="5" t="n">
-        <v>24842</v>
+        <v>24898</v>
       </c>
       <c r="M361" s="3" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="E365" s="4" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F365" s="3" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>14164000</v>
       </c>
       <c r="I365" s="5" t="n">
-        <v>27031</v>
+        <v>26979</v>
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>14164000</v>
       </c>
       <c r="L365" s="5" t="n">
-        <v>27031</v>
+        <v>26979</v>
       </c>
       <c r="M365" s="3" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         </is>
       </c>
       <c r="E368" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>11146000</v>
       </c>
       <c r="I368" s="5" t="n">
-        <v>24769</v>
+        <v>24824</v>
       </c>
       <c r="J368" s="3" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>11146000</v>
       </c>
       <c r="L368" s="5" t="n">
-        <v>24769</v>
+        <v>24824</v>
       </c>
       <c r="M368" s="3" t="inlineStr">
         <is>
@@ -23824,7 +23824,7 @@
         </is>
       </c>
       <c r="E375" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F375" s="3" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>11079000</v>
       </c>
       <c r="I375" s="5" t="n">
-        <v>24620</v>
+        <v>24675</v>
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>11079000</v>
       </c>
       <c r="L375" s="5" t="n">
-        <v>24620</v>
+        <v>24675</v>
       </c>
       <c r="M375" s="3" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         </is>
       </c>
       <c r="E382" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>11033000</v>
       </c>
       <c r="I382" s="5" t="n">
-        <v>24518</v>
+        <v>24572</v>
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>11033000</v>
       </c>
       <c r="L382" s="5" t="n">
-        <v>24518</v>
+        <v>24572</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="E386" s="4" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>14127000</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>26960</v>
+        <v>26909</v>
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>14127000</v>
       </c>
       <c r="L386" s="5" t="n">
-        <v>26960</v>
+        <v>26909</v>
       </c>
       <c r="M386" s="3" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         </is>
       </c>
       <c r="E389" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F389" s="3" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>10987000</v>
       </c>
       <c r="I389" s="5" t="n">
-        <v>24416</v>
+        <v>24470</v>
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>10987000</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>24416</v>
+        <v>24470</v>
       </c>
       <c r="M389" s="3" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         </is>
       </c>
       <c r="E396" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>10954000</v>
       </c>
       <c r="I396" s="5" t="n">
-        <v>24342</v>
+        <v>24396</v>
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>10954000</v>
       </c>
       <c r="L396" s="5" t="n">
-        <v>24342</v>
+        <v>24396</v>
       </c>
       <c r="M396" s="3" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         </is>
       </c>
       <c r="E403" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F403" s="3" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>10922000</v>
       </c>
       <c r="I403" s="5" t="n">
-        <v>24271</v>
+        <v>24325</v>
       </c>
       <c r="J403" s="3" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>10922000</v>
       </c>
       <c r="L403" s="5" t="n">
-        <v>24271</v>
+        <v>24325</v>
       </c>
       <c r="M403" s="3" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         </is>
       </c>
       <c r="E410" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>10889000</v>
       </c>
       <c r="I410" s="5" t="n">
-        <v>24198</v>
+        <v>24252</v>
       </c>
       <c r="J410" s="3" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>10889000</v>
       </c>
       <c r="L410" s="5" t="n">
-        <v>24198</v>
+        <v>24252</v>
       </c>
       <c r="M410" s="3" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         </is>
       </c>
       <c r="E417" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>10856000</v>
       </c>
       <c r="I417" s="5" t="n">
-        <v>24124</v>
+        <v>24178</v>
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>10856000</v>
       </c>
       <c r="L417" s="5" t="n">
-        <v>24124</v>
+        <v>24178</v>
       </c>
       <c r="M417" s="3" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         </is>
       </c>
       <c r="E421" s="4" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>14001000</v>
       </c>
       <c r="I421" s="5" t="n">
-        <v>26719</v>
+        <v>26669</v>
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>14001000</v>
       </c>
       <c r="L421" s="5" t="n">
-        <v>26719</v>
+        <v>26669</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         </is>
       </c>
       <c r="E424" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F424" s="3" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>10824000</v>
       </c>
       <c r="I424" s="5" t="n">
-        <v>24053</v>
+        <v>24107</v>
       </c>
       <c r="J424" s="3" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>10824000</v>
       </c>
       <c r="L424" s="5" t="n">
-        <v>24053</v>
+        <v>24107</v>
       </c>
       <c r="M424" s="3" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         </is>
       </c>
       <c r="E431" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>10759000</v>
       </c>
       <c r="I431" s="5" t="n">
-        <v>23909</v>
+        <v>23962</v>
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>10759000</v>
       </c>
       <c r="L431" s="5" t="n">
-        <v>23909</v>
+        <v>23962</v>
       </c>
       <c r="M431" s="3" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         </is>
       </c>
       <c r="E435" s="4" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F435" s="3" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>13733000</v>
       </c>
       <c r="I435" s="5" t="n">
-        <v>26208</v>
+        <v>26158</v>
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>13733000</v>
       </c>
       <c r="L435" s="5" t="n">
-        <v>26208</v>
+        <v>26158</v>
       </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         </is>
       </c>
       <c r="E438" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F438" s="3" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>10727000</v>
       </c>
       <c r="I438" s="5" t="n">
-        <v>23838</v>
+        <v>23891</v>
       </c>
       <c r="J438" s="3" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>10727000</v>
       </c>
       <c r="L438" s="5" t="n">
-        <v>23838</v>
+        <v>23891</v>
       </c>
       <c r="M438" s="3" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         </is>
       </c>
       <c r="E445" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F445" s="3" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>10695000</v>
       </c>
       <c r="I445" s="5" t="n">
-        <v>23767</v>
+        <v>23820</v>
       </c>
       <c r="J445" s="3" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>10695000</v>
       </c>
       <c r="L445" s="5" t="n">
-        <v>23767</v>
+        <v>23820</v>
       </c>
       <c r="M445" s="3" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         </is>
       </c>
       <c r="E449" s="4" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F449" s="3" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>13569000</v>
       </c>
       <c r="I449" s="5" t="n">
-        <v>25895</v>
+        <v>25846</v>
       </c>
       <c r="J449" s="3" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>13569000</v>
       </c>
       <c r="L449" s="5" t="n">
-        <v>25895</v>
+        <v>25846</v>
       </c>
       <c r="M449" s="3" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         </is>
       </c>
       <c r="E450" s="4" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
@@ -28490,7 +28490,7 @@
         <v>8926000</v>
       </c>
       <c r="I450" s="5" t="n">
-        <v>25073</v>
+        <v>25003</v>
       </c>
       <c r="J450" s="3" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>8926000</v>
       </c>
       <c r="L450" s="5" t="n">
-        <v>25073</v>
+        <v>25003</v>
       </c>
       <c r="M450" s="3" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         </is>
       </c>
       <c r="E451" s="4" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F451" s="3" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>10902000</v>
       </c>
       <c r="I451" s="5" t="n">
-        <v>24227</v>
+        <v>24281</v>
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>10902000</v>
       </c>
       <c r="L451" s="5" t="n">
-        <v>24227</v>
+        <v>24281</v>
       </c>
       <c r="M451" s="3" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         </is>
       </c>
       <c r="E455" s="4" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F455" s="3" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>13467000</v>
       </c>
       <c r="I455" s="5" t="n">
-        <v>25700</v>
+        <v>25651</v>
       </c>
       <c r="J455" s="3" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>13467000</v>
       </c>
       <c r="L455" s="5" t="n">
-        <v>25700</v>
+        <v>25651</v>
       </c>
       <c r="M455" s="3" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         </is>
       </c>
       <c r="E458" s="4" t="n">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F458" s="3" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>20924000</v>
       </c>
       <c r="I458" s="5" t="n">
-        <v>27280</v>
+        <v>27245</v>
       </c>
       <c r="J458" s="3" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>20924000</v>
       </c>
       <c r="L458" s="5" t="n">
-        <v>27280</v>
+        <v>27245</v>
       </c>
       <c r="M458" s="3" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         </is>
       </c>
       <c r="E459" s="4" t="n">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F459" s="3" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>16359000</v>
       </c>
       <c r="I459" s="5" t="n">
-        <v>27220</v>
+        <v>27265</v>
       </c>
       <c r="J459" s="3" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>16359000</v>
       </c>
       <c r="L459" s="5" t="n">
-        <v>27220</v>
+        <v>27265</v>
       </c>
       <c r="M459" s="3" t="inlineStr">
         <is>
@@ -29094,7 +29094,7 @@
         </is>
       </c>
       <c r="E460" s="4" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F460" s="3" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>15162000</v>
       </c>
       <c r="I460" s="5" t="n">
-        <v>25482</v>
+        <v>25440</v>
       </c>
       <c r="J460" s="3" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>15162000</v>
       </c>
       <c r="L460" s="5" t="n">
-        <v>25482</v>
+        <v>25440</v>
       </c>
       <c r="M460" s="3" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         </is>
       </c>
       <c r="E463" s="4" t="n">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F463" s="3" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>19180000</v>
       </c>
       <c r="I463" s="5" t="n">
-        <v>25007</v>
+        <v>24974</v>
       </c>
       <c r="J463" s="3" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>19180000</v>
       </c>
       <c r="L463" s="5" t="n">
-        <v>25007</v>
+        <v>24974</v>
       </c>
       <c r="M463" s="3" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         </is>
       </c>
       <c r="E464" s="4" t="n">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F464" s="3" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>15114000</v>
       </c>
       <c r="I464" s="5" t="n">
-        <v>25148</v>
+        <v>25190</v>
       </c>
       <c r="J464" s="3" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>15114000</v>
       </c>
       <c r="L464" s="5" t="n">
-        <v>25148</v>
+        <v>25190</v>
       </c>
       <c r="M464" s="3" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         </is>
       </c>
       <c r="E469" s="4" t="n">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F469" s="3" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>15024000</v>
       </c>
       <c r="I469" s="5" t="n">
-        <v>24998</v>
+        <v>25040</v>
       </c>
       <c r="J469" s="3" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>15024000</v>
       </c>
       <c r="L469" s="5" t="n">
-        <v>24998</v>
+        <v>25040</v>
       </c>
       <c r="M469" s="3" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         </is>
       </c>
       <c r="E470" s="4" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F470" s="3" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>14981000</v>
       </c>
       <c r="I470" s="5" t="n">
-        <v>25178</v>
+        <v>25136</v>
       </c>
       <c r="J470" s="3" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>14981000</v>
       </c>
       <c r="L470" s="5" t="n">
-        <v>25178</v>
+        <v>25136</v>
       </c>
       <c r="M470" s="3" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         </is>
       </c>
       <c r="E474" s="4" t="n">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F474" s="3" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>14934000</v>
       </c>
       <c r="I474" s="5" t="n">
-        <v>24849</v>
+        <v>24890</v>
       </c>
       <c r="J474" s="3" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>14934000</v>
       </c>
       <c r="L474" s="5" t="n">
-        <v>24849</v>
+        <v>24890</v>
       </c>
       <c r="M474" s="3" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         </is>
       </c>
       <c r="E475" s="4" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F475" s="3" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>14892000</v>
       </c>
       <c r="I475" s="5" t="n">
-        <v>25029</v>
+        <v>24987</v>
       </c>
       <c r="J475" s="3" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>14892000</v>
       </c>
       <c r="L475" s="5" t="n">
-        <v>25029</v>
+        <v>24987</v>
       </c>
       <c r="M475" s="3" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         </is>
       </c>
       <c r="E477" s="4" t="n">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F477" s="3" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>19907000</v>
       </c>
       <c r="I477" s="5" t="n">
-        <v>26865</v>
+        <v>26901</v>
       </c>
       <c r="J477" s="3" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>19907000</v>
       </c>
       <c r="L477" s="5" t="n">
-        <v>26865</v>
+        <v>26901</v>
       </c>
       <c r="M477" s="3" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         </is>
       </c>
       <c r="E479" s="4" t="n">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F479" s="3" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>17187000</v>
       </c>
       <c r="I479" s="5" t="n">
-        <v>29684</v>
+        <v>29633</v>
       </c>
       <c r="J479" s="3" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>17187000</v>
       </c>
       <c r="L479" s="5" t="n">
-        <v>29684</v>
+        <v>29633</v>
       </c>
       <c r="M479" s="3" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         </is>
       </c>
       <c r="E505" s="4" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>18764000</v>
       </c>
       <c r="I505" s="5" t="n">
-        <v>30022</v>
+        <v>29974</v>
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>18764000</v>
       </c>
       <c r="L505" s="5" t="n">
-        <v>30022</v>
+        <v>29974</v>
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         </is>
       </c>
       <c r="E507" s="4" t="n">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F507" s="3" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>20000000</v>
       </c>
       <c r="I507" s="5" t="n">
-        <v>28736</v>
+        <v>28694</v>
       </c>
       <c r="J507" s="3" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         <v>20000000</v>
       </c>
       <c r="L507" s="5" t="n">
-        <v>28736</v>
+        <v>28694</v>
       </c>
       <c r="M507" s="3" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         </is>
       </c>
       <c r="E516" s="4" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F516" s="3" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>11305000</v>
       </c>
       <c r="I516" s="5" t="n">
-        <v>24792</v>
+        <v>24737</v>
       </c>
       <c r="J516" s="3" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>11305000</v>
       </c>
       <c r="L516" s="5" t="n">
-        <v>24792</v>
+        <v>24737</v>
       </c>
       <c r="M516" s="3" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         </is>
       </c>
       <c r="E522" s="4" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F522" s="3" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>11238000</v>
       </c>
       <c r="I522" s="5" t="n">
-        <v>24645</v>
+        <v>24591</v>
       </c>
       <c r="J522" s="3" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>11238000</v>
       </c>
       <c r="L522" s="5" t="n">
-        <v>24645</v>
+        <v>24591</v>
       </c>
       <c r="M522" s="3" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         </is>
       </c>
       <c r="E528" s="4" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F528" s="3" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>11171000</v>
       </c>
       <c r="I528" s="5" t="n">
-        <v>24498</v>
+        <v>24444</v>
       </c>
       <c r="J528" s="3" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>11171000</v>
       </c>
       <c r="L528" s="5" t="n">
-        <v>24498</v>
+        <v>24444</v>
       </c>
       <c r="M528" s="3" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         </is>
       </c>
       <c r="E533" s="4" t="n">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F533" s="3" t="inlineStr">
         <is>
@@ -33636,7 +33636,7 @@
         <v>15946000</v>
       </c>
       <c r="I533" s="5" t="n">
-        <v>30144</v>
+        <v>30201</v>
       </c>
       <c r="J533" s="3" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>15946000</v>
       </c>
       <c r="L533" s="5" t="n">
-        <v>30144</v>
+        <v>30201</v>
       </c>
       <c r="M533" s="3" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         </is>
       </c>
       <c r="E545" s="4" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F545" s="3" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>8826000</v>
       </c>
       <c r="I545" s="5" t="n">
-        <v>24449</v>
+        <v>24517</v>
       </c>
       <c r="J545" s="3" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>8826000</v>
       </c>
       <c r="L545" s="5" t="n">
-        <v>24449</v>
+        <v>24517</v>
       </c>
       <c r="M545" s="3" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         </is>
       </c>
       <c r="E550" s="4" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F550" s="3" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>8816000</v>
       </c>
       <c r="I550" s="5" t="n">
-        <v>24421</v>
+        <v>24489</v>
       </c>
       <c r="J550" s="3" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>8816000</v>
       </c>
       <c r="L550" s="5" t="n">
-        <v>24421</v>
+        <v>24489</v>
       </c>
       <c r="M550" s="3" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         </is>
       </c>
       <c r="E555" s="4" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F555" s="3" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>8802000</v>
       </c>
       <c r="I555" s="5" t="n">
-        <v>24382</v>
+        <v>24450</v>
       </c>
       <c r="J555" s="3" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>8802000</v>
       </c>
       <c r="L555" s="5" t="n">
-        <v>24382</v>
+        <v>24450</v>
       </c>
       <c r="M555" s="3" t="inlineStr">
         <is>
@@ -35593,9 +35593,9 @@
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $880万
-$26,908/呎
+$26,826/呎
 (26年-09月-21日)</t>
         </is>
       </c>
@@ -35608,9 +35608,9 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 714呎 (3房)
+          <t>A | 713呎 (3房)
 $2099万
-$29,392/呎
+$29,433/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -35624,9 +35624,9 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>C | 617呎 (3房)
+          <t>C | 616呎 (3房)
 $1813万
-$29,387/呎
+$29,435/呎
 (22年-05月-24日)</t>
         </is>
       </c>
@@ -35664,9 +35664,9 @@
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $899万
-$27,486/呎
+$27,402/呎
 (26年-05月-22日)</t>
         </is>
       </c>
@@ -35735,9 +35735,9 @@
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $878万
-$26,853/呎
+$26,771/呎
 (26年-01月-20日)</t>
         </is>
       </c>
@@ -35806,9 +35806,9 @@
       </c>
       <c r="I8" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $897万
-$27,431/呎
+$27,348/呎
 (26年-07月-17日)</t>
         </is>
       </c>
@@ -35877,9 +35877,9 @@
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $896万
-$27,401/呎
+$27,317/呎
 (26年-06月-03日)</t>
         </is>
       </c>
@@ -35948,9 +35948,9 @@
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $895万
-$27,373/呎
+$27,290/呎
 (26年-07月-21日)</t>
         </is>
       </c>
@@ -35979,9 +35979,9 @@
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>C | 617呎 (3房)
+          <t>C | 616呎 (3房)
 $1737万
-$28,151/呎
+$28,196/呎
 (22年-05月-24日)</t>
         </is>
       </c>
@@ -36019,9 +36019,9 @@
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $894万
-$27,336/呎
+$27,253/呎
 (26年-07月-31日)</t>
         </is>
       </c>
@@ -36034,9 +36034,9 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 714呎 (3房)
+          <t>A | 713呎 (3房)
 $2004万
-$28,070/呎
+$28,109/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -36090,9 +36090,9 @@
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $892万
-$27,294/呎
+$27,210/呎
 (26年-06月-17日)</t>
         </is>
       </c>
@@ -36105,9 +36105,9 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 714呎 (3房)
+          <t>A | 713呎 (3房)
 $1998万
-$27,987/呎
+$28,027/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -36192,9 +36192,9 @@
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>C | 617呎 (3房)
+          <t>C | 616呎 (3房)
 $1766万
-$28,622/呎
+$28,669/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -36232,9 +36232,9 @@
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $889万
-$27,199/呎
+$27,116/呎
 (26年-06月-12日)</t>
         </is>
       </c>
@@ -36263,9 +36263,9 @@
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>C | 617呎 (3房)
+          <t>C | 616呎 (3房)
 $1755万
-$28,451/呎
+$28,497/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -36303,9 +36303,9 @@
       </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $868万
-$26,547/呎
+$26,466/呎
 (25年-10月-27日)</t>
         </is>
       </c>
@@ -36318,9 +36318,9 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 714呎 (3房)
+          <t>A | 713呎 (3房)
 $2031万
-$28,440/呎
+$28,480/呎
 (22年-05月-18日)</t>
         </is>
       </c>
@@ -36374,9 +36374,9 @@
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $866万
-$26,495/呎
+$26,415/呎
 (25年-06月-17日)</t>
         </is>
       </c>
@@ -36445,9 +36445,9 @@
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $895万
-$27,379/呎
+$27,296/呎
 (26年-06月-12日)</t>
         </is>
       </c>
@@ -36476,9 +36476,9 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>C | 617呎 (3房)
+          <t>C | 616呎 (3房)
 $1692万
-$27,418/呎
+$27,463/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -36516,9 +36516,9 @@
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $881万
-$26,951/呎
+$26,869/呎
 (26年-04月-29日)</t>
         </is>
       </c>
@@ -36547,9 +36547,9 @@
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>C | 617呎 (3房)
+          <t>C | 616呎 (3房)
 $1734万
-$28,112/呎
+$28,157/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -36587,9 +36587,9 @@
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $878万
-$26,841/呎
+$26,759/呎
 (26年-04月-16日)</t>
         </is>
       </c>
@@ -36618,9 +36618,9 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>C | 617呎 (3房)
+          <t>C | 616呎 (3房)
 $1729万
-$28,028/呎
+$28,073/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -36658,9 +36658,9 @@
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $868万
-$26,544/呎
+$26,463/呎
 (22年-06月-17日)</t>
         </is>
       </c>
@@ -36673,9 +36673,9 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>A | 714呎 (3房)
+          <t>A | 713呎 (3房)
 $1998万
-$27,983/呎
+$28,022/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -36729,9 +36729,9 @@
       </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $866万
-$26,489/呎
+$26,409/呎
 (22年-05月-23日)</t>
         </is>
       </c>
@@ -36744,9 +36744,9 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 714呎 (3房)
+          <t>A | 713呎 (3房)
 $1997万
-$27,975/呎
+$28,014/呎
 (22年-05月-25日)</t>
         </is>
       </c>
@@ -36815,9 +36815,9 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 714呎 (3房)
+          <t>A | 713呎 (3房)
 $1986万
-$27,822/呎
+$27,861/呎
 (22年-05月-20日)</t>
         </is>
       </c>
@@ -36831,9 +36831,9 @@
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>C | 617呎 (3房)
+          <t>C | 616呎 (3房)
 $1666万
-$27,010/呎
+$27,054/呎
 (22年-05月-20日)</t>
         </is>
       </c>
@@ -36871,9 +36871,9 @@
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $868万
-$26,532/呎
+$26,451/呎
 (26年-06月-05日)</t>
         </is>
       </c>
@@ -36902,9 +36902,9 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>C | 617呎 (3房)
+          <t>C | 616呎 (3房)
 $1704万
-$27,611/呎
+$27,656/呎
 (22年-05月-20日)</t>
         </is>
       </c>
@@ -36942,9 +36942,9 @@
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $847万
-$25,890/呎
+$25,811/呎
 (26年-03月-19日)</t>
         </is>
       </c>
@@ -36973,9 +36973,9 @@
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>C | 617呎 (3房)
+          <t>C | 616呎 (3房)
 $1686万
-$27,327/呎
+$27,372/呎
 (22年-05月-20日)</t>
         </is>
       </c>
@@ -37028,9 +37028,9 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>A | 714呎 (3房)
+          <t>A | 713呎 (3房)
 $1890万
-$26,468/呎
+$26,505/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -37155,9 +37155,9 @@
       </c>
       <c r="I27" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $857万
-$26,205/呎
+$26,125/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -37226,9 +37226,9 @@
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $842万
-$25,755/呎
+$25,677/呎
 (25年-12月-17日)</t>
         </is>
       </c>
@@ -37297,9 +37297,9 @@
       </c>
       <c r="I29" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $842万
-$25,752/呎
+$25,674/呎
 (25年-08月-27日)</t>
         </is>
       </c>
@@ -37312,9 +37312,9 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>A | 714呎 (3房)
+          <t>A | 713呎 (3房)
 $1835万
-$25,700/呎
+$25,736/呎
 (22年-05月-27日)</t>
         </is>
       </c>
@@ -37368,9 +37368,9 @@
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $856万
-$26,183/呎
+$26,104/呎
 (22年-05月-20日)</t>
         </is>
       </c>
@@ -37383,9 +37383,9 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>A | 714呎 (3房)
+          <t>A | 713呎 (3房)
 $1809万
-$25,333/呎
+$25,369/呎
 (22年-05月-20日)</t>
         </is>
       </c>
@@ -37439,9 +37439,9 @@
       </c>
       <c r="I31" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $832万
-$25,431/呎
+$25,354/呎
 (22年-05月-18日)</t>
         </is>
       </c>
@@ -37454,9 +37454,9 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>A | 714呎 (3房)
+          <t>A | 713呎 (3房)
 $1808万
-$25,319/呎
+$25,355/呎
 (22年-06月-13日)</t>
         </is>
       </c>
@@ -37510,9 +37510,9 @@
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $858万
-$26,239/呎
+$26,159/呎
 (26年-04月-02日)</t>
         </is>
       </c>
@@ -37581,9 +37581,9 @@
       </c>
       <c r="I33" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $839万
-$25,661/呎
+$25,582/呎
 (26年-03月-23日)</t>
         </is>
       </c>
@@ -37645,9 +37645,9 @@
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
-          <t>H | 327呎 (1房)
+          <t>H | 328呎 (1房)
 $858万
-$26,229/呎
+$26,149/呎
 (26年-08月-10日)</t>
         </is>
       </c>
@@ -37848,9 +37848,9 @@
       <c r="E5" s="21" t="inlineStr"/>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>E | 447呎 (2房)
+          <t>E | 446呎 (2房)
 $1176万
-$26,298/呎
+$26,357/呎
 (26年-03月-03日)</t>
         </is>
       </c>
@@ -37974,9 +37974,9 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1174万
-$26,093/呎
+$26,151/呎
 (25年-12月-22日)</t>
         </is>
       </c>
@@ -38037,9 +38037,9 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1212万
-$26,942/呎
+$27,002/呎
 (26年-03月-30日)</t>
         </is>
       </c>
@@ -38100,9 +38100,9 @@
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1167万
-$25,938/呎
+$25,996/呎
 (26年-03月-05日)</t>
         </is>
       </c>
@@ -38163,9 +38163,9 @@
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1164万
-$25,860/呎
+$25,918/呎
 (26年-03月-16日)</t>
         </is>
       </c>
@@ -38194,9 +38194,9 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 524呎 (2房)
+          <t>A | 525呎 (2房)
 $1505万
-$28,727/呎
+$28,672/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -38226,9 +38226,9 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1160万
-$25,782/呎
+$25,840/呎
 (25年-12月-01日)</t>
         </is>
       </c>
@@ -38289,9 +38289,9 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1157万
-$25,704/呎
+$25,762/呎
 (24年-09月-04日)</t>
         </is>
       </c>
@@ -38352,9 +38352,9 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1153万
-$25,629/呎
+$25,686/呎
 (26年-03月-03日)</t>
         </is>
       </c>
@@ -38415,9 +38415,9 @@
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1150万
-$25,551/呎
+$25,608/呎
 (24年-04月-12日)</t>
         </is>
       </c>
@@ -38509,9 +38509,9 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 524呎 (2房)
+          <t>A | 525呎 (2房)
 $1483万
-$28,309/呎
+$28,255/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -38541,9 +38541,9 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1138万
-$25,293/呎
+$25,350/呎
 (24年-04月-02日)</t>
         </is>
       </c>
@@ -38572,9 +38572,9 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 524呎 (2房)
+          <t>A | 525呎 (2房)
 $1514万
-$28,903/呎
+$28,848/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -38667,9 +38667,9 @@
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1131万
-$25,142/呎
+$25,198/呎
 (26年-03月-04日)</t>
         </is>
       </c>
@@ -38698,9 +38698,9 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 524呎 (2房)
+          <t>A | 525呎 (2房)
 $1496万
-$28,553/呎
+$28,499/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -38793,9 +38793,9 @@
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1125万
-$24,993/呎
+$25,049/呎
 (26年-02月-26日)</t>
         </is>
       </c>
@@ -38856,9 +38856,9 @@
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1121万
-$24,918/呎
+$24,973/呎
 (24年-08月-27日)</t>
         </is>
       </c>
@@ -38887,9 +38887,9 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 524呎 (2房)
+          <t>A | 525呎 (2房)
 $1416万
-$27,031/呎
+$26,979/呎
 (22年-05月-19日)</t>
         </is>
       </c>
@@ -38919,9 +38919,9 @@
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1118万
-$24,842/呎
+$24,898/呎
 (24年-04月-25日)</t>
         </is>
       </c>
@@ -38982,9 +38982,9 @@
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1115万
-$24,769/呎
+$24,824/呎
 (25年-12月-19日)</t>
         </is>
       </c>
@@ -39045,9 +39045,9 @@
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1108万
-$24,620/呎
+$24,675/呎
 (26年-02月-04日)</t>
         </is>
       </c>
@@ -39076,9 +39076,9 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>A | 524呎 (2房)
+          <t>A | 525呎 (2房)
 $1413万
-$26,960/呎
+$26,909/呎
 (22年-05月-18日)</t>
         </is>
       </c>
@@ -39108,9 +39108,9 @@
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1103万
-$24,518/呎
+$24,572/呎
 (24年-05月-31日)</t>
         </is>
       </c>
@@ -39171,9 +39171,9 @@
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1099万
-$24,416/呎
+$24,470/呎
 (25年-11月-21日)</t>
         </is>
       </c>
@@ -39234,9 +39234,9 @@
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1095万
-$24,342/呎
+$24,396/呎
 (24年-04月-03日)</t>
         </is>
       </c>
@@ -39297,9 +39297,9 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1092万
-$24,271/呎
+$24,325/呎
 (26年-02月-25日)</t>
         </is>
       </c>
@@ -39360,9 +39360,9 @@
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1089万
-$24,198/呎
+$24,252/呎
 (26年-02月-25日)</t>
         </is>
       </c>
@@ -39391,9 +39391,9 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>A | 524呎 (2房)
+          <t>A | 525呎 (2房)
 $1400万
-$26,719/呎
+$26,669/呎
 (22年-05月-16日)</t>
         </is>
       </c>
@@ -39423,9 +39423,9 @@
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1086万
-$24,124/呎
+$24,178/呎
 (26年-02月-12日)</t>
         </is>
       </c>
@@ -39486,9 +39486,9 @@
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1082万
-$24,053/呎
+$24,107/呎
 (25年-04月-10日)</t>
         </is>
       </c>
@@ -39517,9 +39517,9 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>A | 524呎 (2房)
+          <t>A | 525呎 (2房)
 $1373万
-$26,208/呎
+$26,158/呎
 (23年-12月-19日)</t>
         </is>
       </c>
@@ -39549,9 +39549,9 @@
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1076万
-$23,909/呎
+$23,962/呎
 (26年-03月-19日)</t>
         </is>
       </c>
@@ -39612,9 +39612,9 @@
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1073万
-$23,838/呎
+$23,891/呎
 (26年-03月-20日)</t>
         </is>
       </c>
@@ -39643,9 +39643,9 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>A | 524呎 (2房)
+          <t>A | 525呎 (2房)
 $1357万
-$25,895/呎
+$25,846/呎
 (24年-02月-21日)</t>
         </is>
       </c>
@@ -39675,9 +39675,9 @@
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1070万
-$23,767/呎
+$23,820/呎
 (26年-03月-19日)</t>
         </is>
       </c>
@@ -39706,9 +39706,9 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>A | 524呎 (2房)
+          <t>A | 525呎 (2房)
 $1347万
-$25,700/呎
+$25,651/呎
 (24年-05月-31日)</t>
         </is>
       </c>
@@ -39738,17 +39738,17 @@
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
-          <t>E | 450呎 (2房)
+          <t>E | 449呎 (2房)
 $1090万
-$24,227/呎
+$24,281/呎
 (26年-03月-30日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
         <is>
-          <t>F | 356呎 (1房)
+          <t>F | 357呎 (1房)
 $893万
-$25,073/呎
+$25,003/呎
 (26年-05月-29日)</t>
         </is>
       </c>
@@ -39891,25 +39891,25 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 595呎 (3房)
+          <t>A | 596呎 (3房)
 $1516万
-$25,482/呎
+$25,440/呎
 (24年-03月-19日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>B | 601呎 (3房)
+          <t>B | 600呎 (3房)
 $1636万
-$27,220/呎
+$27,265/呎
 (24年-02月-06日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>C | 767呎 (3房)
+          <t>C | 768呎 (3房)
 $2092万
-$27,280/呎
+$27,245/呎
 (23年-08月-29日)</t>
         </is>
       </c>
@@ -39946,17 +39946,17 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 601呎 (3房)
+          <t>B | 600呎 (3房)
 $1511万
-$25,148/呎
+$25,190/呎
 (24年-04月-19日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>C | 767呎 (3房)
+          <t>C | 768呎 (3房)
 $1918万
-$25,007/呎
+$24,974/呎
 (23年-05月-23日)</t>
         </is>
       </c>
@@ -39985,17 +39985,17 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>A | 595呎 (3房)
+          <t>A | 596呎 (3房)
 $1498万
-$25,178/呎
+$25,136/呎
 (24年-04月-02日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>B | 601呎 (3房)
+          <t>B | 600呎 (3房)
 $1502万
-$24,998/呎
+$25,040/呎
 (24年-04月-17日)</t>
         </is>
       </c>
@@ -40032,17 +40032,17 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>A | 595呎 (3房)
+          <t>A | 596呎 (3房)
 $1489万
-$25,029/呎
+$24,987/呎
 (24年-04月-08日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 601呎 (3房)
+          <t>B | 600呎 (3房)
 $1493万
-$24,849/呎
+$24,890/呎
 (24年-05月-09日)</t>
         </is>
       </c>
@@ -40079,9 +40079,9 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A | 579呎 (3房)
+          <t>A | 580呎 (3房)
 $1719万
-$29,684/呎
+$29,633/呎
 (23年-12月-05日)</t>
         </is>
       </c>
@@ -40095,9 +40095,9 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>C | 741呎 (3房)
+          <t>C | 740呎 (3房)
 $1991万
-$26,865/呎
+$26,901/呎
 (22年-07月-07日)</t>
         </is>
       </c>
@@ -40483,9 +40483,9 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 696呎 (3房)
+          <t>A | 697呎 (3房)
 $2000万
-$28,736/呎
+$28,694/呎
 (23年-08月-11日)</t>
         </is>
       </c>
@@ -40499,9 +40499,9 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>C | 625呎 (2房)
+          <t>C | 626呎 (2房)
 $1876万
-$30,022/呎
+$29,974/呎
 (22年-06月-30日)</t>
         </is>
       </c>
@@ -40730,9 +40730,9 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>D | 456呎 (2房)
+          <t>D | 457呎 (2房)
 $1130万
-$24,792/呎
+$24,737/呎
 (25年-05月-27日)</t>
         </is>
       </c>
@@ -40785,9 +40785,9 @@
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>D | 456呎 (2房)
+          <t>D | 457呎 (2房)
 $1124万
-$24,645/呎
+$24,591/呎
 (25年-09月-09日)</t>
         </is>
       </c>
@@ -40840,9 +40840,9 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>D | 456呎 (2房)
+          <t>D | 457呎 (2房)
 $1117万
-$24,498/呎
+$24,444/呎
 (25年-11月-21日)</t>
         </is>
       </c>
@@ -40887,9 +40887,9 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>C | 529呎 (3房)
+          <t>C | 528呎 (3房)
 $1595万
-$30,144/呎
+$30,201/呎
 (24年-01月-10日)</t>
         </is>
       </c>
@@ -41145,9 +41145,9 @@
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>D | 361呎 (1房)
+          <t>D | 360呎 (1房)
 $883万
-$24,449/呎
+$24,517/呎
 (24年-04月-08日)</t>
         </is>
       </c>
@@ -41192,9 +41192,9 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>D | 361呎 (1房)
+          <t>D | 360呎 (1房)
 $882万
-$24,421/呎
+$24,489/呎
 (25年-01月-07日)</t>
         </is>
       </c>
@@ -41239,9 +41239,9 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>D | 361呎 (1房)
+          <t>D | 360呎 (1房)
 $880万
-$24,382/呎
+$24,450/呎
 (26年-01月-26日)</t>
         </is>
       </c>
